--- a/13_Venture_Capital/_template_VC.xlsx
+++ b/13_Venture_Capital/_template_VC.xlsx
@@ -408,128 +408,132 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -788,54 +792,54 @@
   <dimension ref="B2:C8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -858,178 +862,178 @@
   <dimension ref="A2:G11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="str">
+      <c r="C5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="8" t="str">
         <f aca="false">IFERROR(C5/$C$11,"-")</f>
         <v>-</v>
       </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9" t="n">
+      <c r="E5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10" t="n">
         <f aca="false">C5*E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="str">
+      <c r="C6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8" t="str">
         <f aca="false">IFERROR(C6/$C$11,"-")</f>
         <v>-</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9" t="n">
+      <c r="E6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <f aca="false">C6*E6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="str">
+      <c r="C7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8" t="str">
         <f aca="false">IFERROR(C7/$C$11,"-")</f>
         <v>-</v>
       </c>
-      <c r="E7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="9" t="n">
+      <c r="E7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <f aca="false">C7*E7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="str">
+      <c r="C8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="8" t="str">
         <f aca="false">IFERROR(C8/$C$11,"-")</f>
         <v>-</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9" t="n">
+      <c r="E8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <f aca="false">C8*E8</f>
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="str">
+      <c r="C9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8" t="str">
         <f aca="false">IFERROR(C9/$C$11,"-")</f>
         <v>-</v>
       </c>
-      <c r="E9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="9" t="n">
+      <c r="E9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <f aca="false">C9*E9</f>
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="str">
+      <c r="C10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8" t="str">
         <f aca="false">IFERROR(C10/$C$11,"-")</f>
         <v>-</v>
       </c>
-      <c r="E10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="E10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <f aca="false">C10*E10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <f aca="false">SUM(C5:C10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <f aca="false">SUM(F5:F10)</f>
         <v>0</v>
       </c>
@@ -1053,110 +1057,110 @@
   <dimension ref="B2:F11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="13" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="C5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <f aca="false">C5+C6</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="s">
+      <c r="C6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="15" t="str">
+      <c r="F6" s="16" t="str">
         <f aca="false">IFERROR(C5/C8,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="C7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="17" t="str">
+      <c r="F7" s="18" t="str">
         <f aca="false">IFERROR(C6/F6,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14" t="s">
+      <c r="C8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="17" t="str">
+      <c r="F8" s="18" t="str">
         <f aca="false">IFERROR(C7*(C8+F7),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="19" t="str">
+      <c r="F9" s="20" t="str">
         <f aca="false">IFERROR(C8+F7+F8,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="20" t="str">
+      <c r="F10" s="21" t="str">
         <f aca="false">IFERROR(F7/F9,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="20" t="str">
+      <c r="F11" s="21" t="str">
         <f aca="false">IFERROR(1-C8/F9,"-")</f>
         <v>-</v>
       </c>
@@ -1180,86 +1184,86 @@
   <dimension ref="B2:F9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="C5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="21" t="str">
+      <c r="F5" s="22" t="str">
         <f aca="false">'Round Modeling'!F6</f>
         <v>-</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="s">
+      <c r="C6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="15" t="str">
+      <c r="F6" s="16" t="str">
         <f aca="false">IFERROR(C6/'Round Modeling'!C8,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="C7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="15" t="str">
+      <c r="F7" s="16" t="str">
         <f aca="false">IFERROR(F5*(1-C7),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="23" t="n">
         <f aca="false">IFERROR(MIN(IF(ISNUMBER(F5),F5,9E+099),IF(ISNUMBER(F6),F6,9E+099),IF(ISNUMBER(F7),F7,9E+099)),"-")</f>
         <v>9E+099</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <f aca="false">IFERROR(C5/F8,"-")</f>
         <v>0</v>
       </c>
@@ -1283,185 +1287,185 @@
   <dimension ref="A2:H15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="15" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="24" t="n">
         <f aca="false">'Cap Table'!F10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <f aca="false">C5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="24" t="str">
+      <c r="E5" s="25" t="str">
         <f aca="false">IFERROR('Cap Table'!D10,"-")</f>
         <v>-</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <f aca="false">MIN($C$15,D5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="9" t="str">
+      <c r="G5" s="10" t="str">
         <f aca="false">IFERROR($C$15*E5,"-")</f>
         <v>-</v>
       </c>
-      <c r="H5" s="25" t="n">
+      <c r="H5" s="26" t="n">
         <f aca="false">IF($C$15&gt;SUM($D$5:$D$7),G5,F5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <f aca="false">'Cap Table'!F9</f>
         <v>0</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="10" t="n">
         <f aca="false">C6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="24" t="str">
+      <c r="E6" s="25" t="str">
         <f aca="false">IFERROR('Cap Table'!D9,"-")</f>
         <v>-</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <f aca="false">MIN(MAX($C$15-F5,0),D6)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="9" t="str">
+      <c r="G6" s="10" t="str">
         <f aca="false">IFERROR($C$15*E6,"-")</f>
         <v>-</v>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="26" t="n">
         <f aca="false">IF($C$15&gt;SUM($D$5:$D$7),G6,F6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="24" t="n">
         <f aca="false">'Cap Table'!F8</f>
         <v>0</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <f aca="false">C7</f>
         <v>0</v>
       </c>
-      <c r="E7" s="24" t="str">
+      <c r="E7" s="25" t="str">
         <f aca="false">IFERROR('Cap Table'!D8,"-")</f>
         <v>-</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <f aca="false">MIN(MAX($C$15-F5-F6,0),D7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="9" t="str">
+      <c r="G7" s="10" t="str">
         <f aca="false">IFERROR($C$15*E7,"-")</f>
         <v>-</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="26" t="n">
         <f aca="false">IF($C$15&gt;SUM($D$5:$D$7),G7,F7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="24" t="n">
         <f aca="false">'Cap Table'!F5+'Cap Table'!F6</f>
         <v>0</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="10" t="n">
         <f aca="false">C8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="24" t="str">
+      <c r="E8" s="25" t="str">
         <f aca="false">IFERROR('Cap Table'!D5+'Cap Table'!D6,"-")</f>
         <v>-</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <f aca="false">MAX(0,$C$15-F5-F6-F7)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="9" t="str">
+      <c r="G8" s="10" t="str">
         <f aca="false">IFERROR($C$15*E8,"-")</f>
         <v>-</v>
       </c>
-      <c r="H8" s="25" t="n">
+      <c r="H8" s="26" t="n">
         <f aca="false">IF($C$15&gt;SUM($D$5:$D$7),G8,F8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="2" t="str">
+      <c r="C10" s="3" t="str">
         <f aca="false">IF($C$15&gt;SUM(D5:D7),"YES — use as-converted","NO — use pref-stack")</f>
         <v>NO — use pref-stack</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <f aca="false">SUM(H5:H8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="27" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="27" t="n">
+      <c r="C15" s="28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1484,196 +1488,196 @@
   <dimension ref="A2:G12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="15" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="28" t="s">
+      <c r="B5" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="28" t="s">
+      <c r="B6" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="29" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="28" t="s">
+      <c r="B7" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="29" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="28" t="s">
+      <c r="B8" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="29" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="B9" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="29" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="28" t="s">
+      <c r="B10" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="29" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="28" t="s">
+      <c r="B11" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="29" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="28" t="s">
+      <c r="B12" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="29" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1696,104 +1700,104 @@
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/13_Venture_Capital/_template_VC.xlsx
+++ b/13_Venture_Capital/_template_VC.xlsx
@@ -13,8 +13,11 @@
     <sheet name="Round Modeling" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="SAFE Conversion" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Exit Waterfall" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Comparable Financings" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="RefreshLog" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Participating Preferred" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Comparable Financings" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Sources" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Checks" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="RefreshLog" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="120">
   <si>
     <t xml:space="preserve">[COMPANY] — Venture Capital Model</t>
   </si>
@@ -211,6 +214,51 @@
     <t xml:space="preserve">Total exit proceeds</t>
   </si>
   <si>
+    <t xml:space="preserve">Capped Participating Preferred: the Payout "Kink"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A structurally different preference from the 1x non-participating pref on the Exit Waterfall tab: participating preferred takes its liquidation pref off the top AND THEN ALSO shares pro-rata in what's left, alongside common -- "double dipping." A cap limits total return to a multiple of invested capital; once uncapped participation would exceed the cap, a rational holder converts to common instead and gives up the pref entirely. That crossover is the kink.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invested amount ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidation preference multiple (x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participation cap (total return multiple, x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As-converted ownership % (this class's fully-diluted share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit enterprise value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidation preference ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncapped participating payout (pref + pro-rata of the rest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capped payout (MIN of uncapped, cap x invested)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As-converted payout (forgo pref, straight pro-rata of total)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual payout (rational holder takes the higher)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Election</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective multiple at the cap crossover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Above the exit value where as-converted alone would already return more than the cap, participating preferred is strictly worse than plain common -- the cap exists to bound the PREFERRED holder's return, not to help them</t>
+  </si>
+  <si>
     <t xml:space="preserve">Comparable Financings</t>
   </si>
   <si>
@@ -230,6 +278,102 @@
   </si>
   <si>
     <t xml:space="preserve">Lead investor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each material assumption or convention in this model comes from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption / convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capped participating preferred: pref + pro-rata, capped, MAX vs. as-converted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard VC/PE preferred-stock term-sheet mechanics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-class simplification -- models one participating class against 'everyone else' as a pool, not a full multi-class cascade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x non-participating pref-stack vs. as-converted exit waterfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard VC exit-waterfall mechanics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole-cap-table regime switch (see the tab's own note) -- an approximation of the true class-by-class conversion election</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAFE conversion: lower of cap price, discount price, round price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard Y Combinator SAFE / convertible-note conversion mechanics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumes a single SAFE with both cap and discount -- some SAFEs have only one or the other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre/post-money round math with option-pool top-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard VC financing-round mechanics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumes the option pool top-up is sized post-money and dilutes pre-round holders only, the most common (but not universal) convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live reconciliation identities -- independent of the model's own formulas, must tie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passes when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capped payout never exceeds the cap (invested x cap multiple)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE -- the cap is an upper bound by construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the largest exit value, the rational holder converts to common (cap made pref strictly worse)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE at the default $500mm exit -- confirms the cap actually binds somewhere in the sweep, not just in theory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the smallest exit value, the rational holder takes pref+participation (pref is still worth more)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE at the default $20mm exit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VC exit waterfall total distributed ties to total exit proceeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) once exit proceeds are populated</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -251,12 +395,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="168" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="169" formatCode="0.0\x"/>
+    <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -408,7 +554,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -525,6 +671,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -533,7 +695,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -854,6 +1024,124 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:F14"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -1485,14 +1773,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:G12"/>
+  <dimension ref="B2:I19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1500,185 +1787,282 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="5" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="C6" s="14" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C7" s="29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="C8" s="29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="C9" s="17" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>2</v>
+      <c r="C11" s="30" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>50000000</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>0</v>
+        <v>80000000</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>2</v>
+        <v>100000000</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="H11" s="30" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="I11" s="30" t="n">
+        <v>500000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>2</v>
+      <c r="B12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <f aca="false">$C$6*$C$7</f>
+        <v>10000000</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <f aca="false">$C$6*$C$7</f>
+        <v>10000000</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <f aca="false">$C$6*$C$7</f>
+        <v>10000000</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <f aca="false">$C$6*$C$7</f>
+        <v>10000000</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <f aca="false">$C$6*$C$7</f>
+        <v>10000000</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <f aca="false">$C$6*$C$7</f>
+        <v>10000000</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <f aca="false">$C$6*$C$7</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <f aca="false">C12+$C$9*MAX(C11-C12,0)</f>
+        <v>12000000</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <f aca="false">D12+$C$9*MAX(D11-D12,0)</f>
+        <v>18000000</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <f aca="false">E12+$C$9*MAX(E11-E12,0)</f>
+        <v>24000000</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <f aca="false">F12+$C$9*MAX(F11-F12,0)</f>
+        <v>28000000</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <f aca="false">G12+$C$9*MAX(G11-G12,0)</f>
+        <v>38000000</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <f aca="false">H12+$C$9*MAX(H11-H12,0)</f>
+        <v>48000000</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <f aca="false">I12+$C$9*MAX(I11-I12,0)</f>
+        <v>108000000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <f aca="false">MIN(C13,$C$6*$C$8)</f>
+        <v>12000000</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <f aca="false">MIN(D13,$C$6*$C$8)</f>
+        <v>18000000</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <f aca="false">MIN(E13,$C$6*$C$8)</f>
+        <v>24000000</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <f aca="false">MIN(F13,$C$6*$C$8)</f>
+        <v>28000000</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <f aca="false">MIN(G13,$C$6*$C$8)</f>
+        <v>30000000</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <f aca="false">MIN(H13,$C$6*$C$8)</f>
+        <v>30000000</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <f aca="false">MIN(I13,$C$6*$C$8)</f>
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <f aca="false">$C$9*C11</f>
+        <v>4000000</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <f aca="false">$C$9*D11</f>
+        <v>10000000</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <f aca="false">$C$9*E11</f>
+        <v>16000000</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <f aca="false">$C$9*F11</f>
+        <v>20000000</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <f aca="false">$C$9*G11</f>
+        <v>30000000</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <f aca="false">$C$9*H11</f>
+        <v>40000000</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <f aca="false">$C$9*I11</f>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="26" t="n">
+        <f aca="false">MAX(C14,C15)</f>
+        <v>12000000</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <f aca="false">MAX(D14,D15)</f>
+        <v>18000000</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <f aca="false">MAX(E14,E15)</f>
+        <v>24000000</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <f aca="false">MAX(F14,F15)</f>
+        <v>28000000</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <f aca="false">MAX(G14,G15)</f>
+        <v>30000000</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <f aca="false">MAX(H14,H15)</f>
+        <v>40000000</v>
+      </c>
+      <c r="I16" s="26" t="n">
+        <f aca="false">MAX(I14,I15)</f>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="31" t="str">
+        <f aca="false">IF(C16=C15,"CONVERT TO COMMON","TAKE PREF + PARTICIPATE")</f>
+        <v>TAKE PREF + PARTICIPATE</v>
+      </c>
+      <c r="D17" s="31" t="str">
+        <f aca="false">IF(D16=D15,"CONVERT TO COMMON","TAKE PREF + PARTICIPATE")</f>
+        <v>TAKE PREF + PARTICIPATE</v>
+      </c>
+      <c r="E17" s="31" t="str">
+        <f aca="false">IF(E16=E15,"CONVERT TO COMMON","TAKE PREF + PARTICIPATE")</f>
+        <v>TAKE PREF + PARTICIPATE</v>
+      </c>
+      <c r="F17" s="31" t="str">
+        <f aca="false">IF(F16=F15,"CONVERT TO COMMON","TAKE PREF + PARTICIPATE")</f>
+        <v>TAKE PREF + PARTICIPATE</v>
+      </c>
+      <c r="G17" s="31" t="str">
+        <f aca="false">IF(G16=G15,"CONVERT TO COMMON","TAKE PREF + PARTICIPATE")</f>
+        <v>CONVERT TO COMMON</v>
+      </c>
+      <c r="H17" s="31" t="str">
+        <f aca="false">IF(H16=H15,"CONVERT TO COMMON","TAKE PREF + PARTICIPATE")</f>
+        <v>CONVERT TO COMMON</v>
+      </c>
+      <c r="I17" s="31" t="str">
+        <f aca="false">IF(I16=I15,"CONVERT TO COMMON","TAKE PREF + PARTICIPATE")</f>
+        <v>CONVERT TO COMMON</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="32" t="n">
+        <f aca="false">IFERROR(C8,"-")</f>
+        <v>3</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1697,107 +2081,401 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F14"/>
+  <dimension ref="A2:G12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>72</v>
+        <v>81</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
+      <c r="B5" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
+      <c r="B6" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
+      <c r="B7" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
+      <c r="B8" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
+      <c r="B9" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
+      <c r="B10" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
+      <c r="B11" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
+      <c r="B12" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="37" t="b">
+        <f aca="false">IF(MAX('Participating Preferred'!C14:I14)&lt;=('Participating Preferred'!$C$6*'Participating Preferred'!$C$8)*1.0000001,TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="37" t="b">
+        <f aca="false">IF('Participating Preferred'!I17="CONVERT TO COMMON",TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="37" t="b">
+        <f aca="false">IF('Participating Preferred'!C17="TAKE PREF + PARTICIPATE",TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="37" t="n">
+        <f aca="false">'Exit Waterfall'!C11-'Exit Waterfall'!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>114</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
